--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SEC_01_CHECK_LIST_405.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE405_Introduction to Deep Learning/SEC_01_CHECK_LIST_405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE405_Introduction to Deep Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609291BA-4114-4248-8F7A-B51D6D8C329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351F6730-44C4-4185-B3CD-558D0AFF7AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีราชมงคลล้านนา เชียงราย</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>ล</t>
+  </si>
+  <si>
+    <t>ข</t>
   </si>
 </sst>
 </file>
@@ -620,7 +623,9 @@
       <c r="M5" s="2">
         <v>2</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" s="2">
+        <v>3</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -661,7 +666,9 @@
       <c r="M6" s="2">
         <v>20</v>
       </c>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
@@ -702,7 +709,9 @@
       <c r="M7" s="2">
         <v>9</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2">
+        <v>10</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
@@ -747,7 +756,9 @@
       <c r="M8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -792,7 +803,9 @@
       <c r="M9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -837,7 +850,9 @@
       <c r="M10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -882,7 +897,9 @@
       <c r="M11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
